--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -3313,7 +3313,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3322,31 +3322,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3358,7 +3358,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3367,31 +3367,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3412,31 +3412,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3448,7 +3448,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3457,31 +3457,31 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3493,7 +3493,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3502,31 +3502,31 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3538,7 +3538,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3547,31 +3547,31 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3583,7 +3583,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3601,22 +3601,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3628,7 +3628,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3637,31 +3637,31 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3673,7 +3673,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3682,31 +3682,31 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3727,31 +3727,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3763,7 +3763,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3772,31 +3772,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3808,7 +3808,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3817,31 +3817,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3853,40 +3853,38 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>76</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3898,7 +3896,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3907,31 +3905,31 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3943,7 +3941,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3952,31 +3950,31 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3988,7 +3986,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3997,31 +3995,31 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4033,7 +4031,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4042,31 +4040,31 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4078,7 +4076,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4087,31 +4085,31 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4123,7 +4121,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4132,31 +4130,31 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4168,7 +4166,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4177,31 +4175,31 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4213,7 +4211,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4222,31 +4220,31 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4258,7 +4256,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4267,31 +4265,31 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-dxp-enterprises-dxpe.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4303,7 +4301,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4312,31 +4310,31 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4348,7 +4346,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4357,31 +4355,31 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4393,7 +4391,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4402,31 +4400,31 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4438,7 +4436,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4447,31 +4445,31 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4483,7 +4481,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4492,31 +4490,31 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4528,7 +4526,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4537,31 +4535,31 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4573,7 +4571,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4582,31 +4580,31 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4618,7 +4616,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4627,31 +4625,31 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4663,7 +4661,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4672,31 +4670,31 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4708,7 +4706,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4717,31 +4715,31 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4753,7 +4751,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4762,31 +4760,31 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4798,7 +4796,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4807,31 +4805,31 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4843,7 +4841,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4852,31 +4850,31 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4888,7 +4886,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4897,31 +4895,31 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4933,7 +4931,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4942,31 +4940,31 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4978,7 +4976,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4987,31 +4985,31 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5023,7 +5021,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5032,7 +5030,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -5041,22 +5039,22 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5068,7 +5066,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5077,31 +5075,31 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5113,7 +5111,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5122,31 +5120,31 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5158,7 +5156,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5167,31 +5165,31 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-comfort-systems-usa-fix.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5203,7 +5201,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5212,31 +5210,31 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5248,7 +5246,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5257,31 +5255,31 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-comfort-systems-usa-fix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5293,7 +5291,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5302,31 +5300,31 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5338,7 +5336,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5347,31 +5345,31 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5383,7 +5381,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5392,31 +5390,31 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5428,7 +5426,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5437,31 +5435,31 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5473,7 +5471,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5482,31 +5480,31 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5518,7 +5516,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5527,31 +5525,31 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5563,7 +5561,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5572,31 +5570,31 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5608,7 +5606,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5617,31 +5615,31 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5653,7 +5651,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5662,31 +5660,31 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5698,7 +5696,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5707,31 +5705,31 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5743,7 +5741,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5752,31 +5750,31 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5788,7 +5786,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5797,31 +5795,31 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5833,7 +5831,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5842,31 +5840,31 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5878,7 +5876,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5887,31 +5885,31 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5923,7 +5921,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5932,31 +5930,31 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5968,7 +5966,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5977,31 +5975,31 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6013,7 +6011,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6022,31 +6020,31 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6058,7 +6056,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6067,31 +6065,31 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6103,7 +6101,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6112,31 +6110,31 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6148,7 +6146,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6157,31 +6155,31 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6193,7 +6191,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6202,31 +6200,31 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6238,7 +6236,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6247,31 +6245,31 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6283,7 +6281,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6292,31 +6290,31 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6328,7 +6326,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6337,7 +6335,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -6346,22 +6344,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6373,7 +6371,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6382,31 +6380,31 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6418,7 +6416,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6427,7 +6425,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -6436,22 +6434,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6463,7 +6461,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6472,31 +6470,31 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-mega-fortune-mgrt.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6508,7 +6506,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6517,31 +6515,31 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6553,7 +6551,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6562,31 +6560,31 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-mega-fortune-mgrt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6598,7 +6596,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6607,31 +6605,31 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6643,7 +6641,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6652,31 +6650,31 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6688,7 +6686,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6697,31 +6695,31 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6733,90 +6731,90 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>대기</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>
@@ -6832,7 +6830,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -6856,7 +6854,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,40 +483,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-crowdstrike-holdings-crwd.htm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -528,35 +528,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -573,11 +573,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -586,22 +586,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,35 +618,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -663,35 +663,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,35 +753,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -798,35 +798,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -843,35 +843,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SUTNY</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-sumitomo-mitsui-trust-group-adr-sutny.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SUTNY</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -888,35 +888,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -933,35 +933,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,35 +1023,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 35</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-iovance-biotherapeutics-iova.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-iovance-biotherapeutics-iova.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1113,35 +1113,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-okta-cl-a-okta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,35 +1248,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,35 +1293,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-gerdau-adr-ggb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1383,40 +1383,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-sumitomo-mitsui-financial-group-adr-smfg.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>SUTNY</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1428,40 +1428,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>BGC</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1473,40 +1473,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BGC</t>
+          <t>VIST</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-bgc-group-cl-a-bgc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-vista-energy-adr-vist.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BGC</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1518,35 +1518,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1563,35 +1563,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 34</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>CBWTF</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-auxly-cannabis-group-cbwtf.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>CBWTF</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1608,35 +1608,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1653,35 +1653,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1698,35 +1698,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 17</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1743,35 +1743,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1788,40 +1788,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1833,40 +1833,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-semtech-smtc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-openlane-opln.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>ACVA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1878,35 +1878,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-northern-trust-ntrs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1923,40 +1923,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>GGB</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1968,35 +1968,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-camden-national-cac.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2058,35 +2058,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2103,35 +2103,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2148,35 +2148,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2193,40 +2193,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>QUAD</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2238,35 +2238,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2296,27 +2296,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-camden-national-cac.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2328,35 +2328,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 36</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2373,35 +2373,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2418,35 +2418,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2463,40 +2463,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 40</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-stagwell-stgw.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2508,35 +2508,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>EJPRY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-east-japan-railway-adr-ejpry.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>EJPRY</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2553,35 +2553,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 22</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2598,35 +2598,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2643,35 +2643,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2688,35 +2688,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 25</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2733,35 +2733,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 55</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ACVA</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-acv-auctions-acva.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ACVA</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2778,35 +2778,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2823,35 +2823,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2868,35 +2868,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>EJPRY</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-east-japan-railway-adr-ejpry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>EJPRY</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2913,35 +2913,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2958,35 +2958,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 22</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3003,40 +3003,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 33</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3048,35 +3048,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 31</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-celestica-cls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3093,40 +3093,40 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 28</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CBWTF</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-auxly-cannabis-group-cbwtf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CBWTF</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3138,35 +3138,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 28</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3183,35 +3183,35 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>QUAD</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quadgraphics-quad.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>QUAD</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3228,40 +3228,38 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>62</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oneok-oke.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3273,35 +3271,33 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>63</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3313,40 +3309,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3358,40 +3354,40 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3403,40 +3399,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3448,85 +3444,85 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 23</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3538,40 +3534,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3583,16 +3579,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3601,22 +3597,22 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3628,40 +3624,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3673,85 +3669,85 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3763,40 +3759,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 30</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3808,40 +3804,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3853,38 +3849,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>▲ 20</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>96</v>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3896,40 +3894,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3941,40 +3939,40 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3986,40 +3984,40 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 37</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,40 +4029,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4076,40 +4074,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4121,40 +4119,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 42</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4166,40 +4164,40 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4211,40 +4209,40 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4256,40 +4254,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 35</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4301,40 +4299,40 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4346,16 +4344,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4364,22 +4362,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4391,40 +4389,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 17</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4436,40 +4434,40 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4481,16 +4479,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4499,22 +4497,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4526,40 +4524,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4571,40 +4569,40 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 37</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4616,40 +4614,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 26</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4661,40 +4659,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4706,40 +4704,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 67</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4751,40 +4749,40 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4796,7 +4794,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4805,31 +4803,31 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4841,40 +4839,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 46</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4886,40 +4884,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4931,40 +4929,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4976,40 +4974,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5021,85 +5019,85 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 44</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>SANM</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sanmina-sanm.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 30</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5111,40 +5109,38 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>107</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-dxp-enterprises-dxpe.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5156,40 +5152,40 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-comfort-systems-usa-fix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5201,16 +5197,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -5219,22 +5215,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5246,40 +5242,40 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5291,40 +5287,40 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 27</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5336,40 +5332,40 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5381,40 +5377,40 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5426,40 +5422,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5471,40 +5467,40 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5516,40 +5512,40 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5561,40 +5557,40 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5606,16 +5602,16 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -5624,22 +5620,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5651,40 +5647,40 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5696,40 +5692,40 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5741,40 +5737,40 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5786,40 +5782,40 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5831,85 +5827,85 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5921,40 +5917,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5966,40 +5962,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6011,40 +6007,40 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6056,40 +6052,40 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6101,40 +6097,40 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6146,40 +6142,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6191,130 +6187,130 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>MGRT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 42</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 29</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6326,40 +6322,40 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6371,40 +6367,40 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6416,12 +6412,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -6461,85 +6457,85 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-mega-fortune-mgrt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6551,40 +6547,40 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 29</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6596,40 +6592,40 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6641,40 +6637,40 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6686,40 +6682,40 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 41</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6731,135 +6727,135 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,40 +483,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-crowdstrike-holdings-crwd.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -536,27 +536,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -573,35 +573,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-crowdstrike-holdings-crwd.htm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,35 +618,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -663,35 +663,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -708,35 +708,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -753,35 +753,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -798,40 +798,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -843,40 +843,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eog-resources-eog.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>VIST</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -888,35 +888,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -933,35 +933,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,35 +1023,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▲ 35</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1076,27 +1076,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-iovance-biotherapeutics-iova.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1113,35 +1113,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1158,35 +1158,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,35 +1248,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,35 +1293,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aveanna-healthcare-holdings-avah.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1338,40 +1338,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>SUTNY</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-sumitomo-mitsui-trust-group-adr-sutny.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>SMFG</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1383,40 +1383,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-sumitomo-mitsui-financial-group-adr-smfg.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SUTNY</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BGC</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1473,40 +1473,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VIST</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-vista-energy-adr-vist.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1518,40 +1518,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1563,40 +1563,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▲ 34</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CBWTF</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-auxly-cannabis-group-cbwtf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-visa-cl-a-v.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CBWTF</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1608,40 +1608,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cocacola-consolidated-coke.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1653,40 +1653,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1698,35 +1698,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▲ 17</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1743,35 +1743,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1788,40 +1788,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-camden-national-cac.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1833,40 +1833,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▲ 54</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-openlane-opln.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ACVA</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1878,35 +1878,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CBWTF</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-auxly-cannabis-group-cbwtf.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CBWTF</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1923,40 +1923,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>GGB</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1968,35 +1968,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-camden-national-cac.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2013,35 +2013,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-enova-international-enva.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2058,35 +2058,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2103,40 +2103,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>EJPRY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2148,35 +2148,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2193,40 +2193,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>QUAD</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2238,11 +2238,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2283,40 +2283,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 23</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2328,35 +2328,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 36</t>
+          <t>▲ 23</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2373,40 +2373,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>ACVA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-acv-auctions-acva.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>OPLN</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2418,11 +2418,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2431,22 +2431,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2463,40 +2463,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 40</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-stagwell-stgw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2508,35 +2508,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>EJPRY</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-east-japan-railway-adr-ejpry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>EJPRY</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2553,35 +2553,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▼ 22</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2598,35 +2598,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2643,35 +2643,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2688,11 +2688,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 25</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2701,22 +2701,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2733,35 +2733,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 55</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2778,35 +2778,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2823,35 +2823,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2868,11 +2868,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2881,27 +2881,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>STGW</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2913,35 +2913,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2958,35 +2958,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 22</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3003,35 +3003,35 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>TTNDY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-techtronic-industries-adr-ttndy.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3048,40 +3048,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 31</t>
+          <t>▼ 23</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ENVA</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3093,35 +3093,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▼ 28</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3138,35 +3138,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▲ 28</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3183,35 +3183,35 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3228,10 +3228,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>▲ 17</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>79</v>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>energy</t>
@@ -3239,27 +3241,27 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oneok-oke.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3271,33 +3273,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>▲ 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>72</v>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3314,35 +3318,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3359,35 +3363,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3404,35 +3408,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3449,40 +3453,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3494,35 +3498,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▲ 23</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3539,35 +3543,35 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▲ 21</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3584,35 +3588,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3629,35 +3633,35 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3674,40 +3678,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3719,35 +3723,35 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3764,35 +3768,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▼ 30</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3809,35 +3813,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3854,35 +3858,35 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3899,35 +3903,35 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 49</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3944,35 +3948,35 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3989,35 +3993,35 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▼ 37</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4034,40 +4038,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4079,35 +4083,35 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4124,35 +4128,35 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 42</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4169,35 +4173,35 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4214,35 +4218,35 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4259,35 +4263,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▼ 35</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4304,35 +4308,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4349,35 +4353,35 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4394,35 +4398,35 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▲ 17</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4434,45 +4438,45 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>GATX</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-gatx-gatx.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4484,35 +4488,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4529,11 +4533,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -4542,22 +4546,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4574,40 +4578,40 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▼ 37</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>UROY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4619,35 +4623,35 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▲ 26</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4659,40 +4663,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4704,40 +4708,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 67</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4754,35 +4758,35 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4799,35 +4803,35 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 27</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4844,35 +4848,35 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▼ 46</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4884,40 +4888,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4929,40 +4933,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4979,35 +4983,35 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-dxp-enterprises-dxpe.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5024,40 +5028,40 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 44</t>
+          <t>▼ 34</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sanmina-sanm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5069,78 +5073,80 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 30</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>SANM</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>▼ 10</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>94</v>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-dxp-enterprises-dxpe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5152,40 +5158,40 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5202,35 +5208,35 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5247,35 +5253,35 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5287,40 +5293,40 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5337,35 +5343,35 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5382,35 +5388,35 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 26</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5427,35 +5433,35 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5472,35 +5478,35 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5517,35 +5523,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-uranium-royalty-uroy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5562,11 +5568,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -5575,27 +5581,27 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-bill-holdings-bill.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5607,35 +5613,35 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 27</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5652,11 +5658,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -5665,22 +5671,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5697,35 +5703,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5742,35 +5748,35 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5787,35 +5793,35 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5832,40 +5838,40 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5877,35 +5883,35 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5922,35 +5928,35 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5967,35 +5973,35 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6012,35 +6018,35 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6057,35 +6063,35 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6102,35 +6108,35 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6147,35 +6153,35 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6192,40 +6198,40 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>MGRT</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6237,40 +6243,40 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▼ 42</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6282,35 +6288,35 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▼ 29</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6327,35 +6333,35 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6372,35 +6378,35 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6417,11 +6423,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -6430,27 +6436,27 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>LKNCY</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-luckin-coffee-adr-lkncy.htm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -6462,40 +6468,40 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6507,11 +6513,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -6520,22 +6526,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6552,35 +6558,35 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▼ 29</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6597,35 +6603,35 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6642,35 +6648,35 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6687,11 +6693,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>▼ 41</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -6700,22 +6706,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6740,27 +6746,27 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6777,11 +6783,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -6822,11 +6828,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,11 +483,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -528,11 +528,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -573,11 +573,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -591,22 +591,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>CRWD</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-crowdstrike-holdings-crwd.htm</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -618,11 +618,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -671,27 +671,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -708,35 +708,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -753,11 +753,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -766,22 +766,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -798,40 +798,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -843,40 +843,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eog-resources-eog.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>VIST</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -888,35 +888,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -933,40 +933,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-salesforce-crm.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,35 +1023,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1113,11 +1113,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1158,40 +1158,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-iovance-biotherapeutics-iova.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,35 +1248,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,35 +1293,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1338,40 +1338,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SUTNY</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-sumitomo-mitsui-trust-group-adr-sutny.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1383,35 +1383,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 39</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1473,40 +1473,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>CBWTF</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1518,35 +1518,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>VBNK</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1563,40 +1563,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-visa-cl-a-v.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1608,11 +1608,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1653,35 +1653,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-berkshire-hathaway-cl-b-brk.b.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1711,22 +1711,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>SUTNY</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-sumitomo-mitsui-trust-group-adr-sutny.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>SUTNY</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1743,40 +1743,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>V</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1788,40 +1788,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 21</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-camden-national-cac.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1833,35 +1833,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 54</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1878,40 +1878,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CBWTF</t>
+          <t>PLMR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-auxly-cannabis-group-cbwtf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palomar-holdings-plmr.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CBWTF</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1923,40 +1923,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>BGC</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-bgc-group-cl-a-bgc.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1968,35 +1968,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-eton-pharmaceuticals-eton.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2013,35 +2013,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2058,35 +2058,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2103,35 +2103,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>EJPRY</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2148,35 +2148,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2193,40 +2193,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2238,40 +2238,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-semtech-smtc.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2283,40 +2283,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 23</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>CAC</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2328,35 +2328,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 23</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2373,40 +2373,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ACVA</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-acv-auctions-acva.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>OPLN</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2418,35 +2418,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2463,35 +2463,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2508,35 +2508,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2553,40 +2553,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 27</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2598,35 +2598,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2643,35 +2643,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 38</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2688,35 +2688,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2733,35 +2733,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2778,80 +2778,80 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>ACVA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2863,85 +2863,85 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>TTNDY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-techtronic-industries-adr-ttndy.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>STGW</t>
+          <t>TTNDY</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2953,40 +2953,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 20</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2998,175 +2998,175 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TTNDY</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-techtronic-industries-adr-ttndy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▼ 23</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ENVA</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3178,40 +3178,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3223,40 +3223,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▲ 17</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3268,40 +3268,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3313,16 +3313,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3358,40 +3358,40 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 17</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3403,40 +3403,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3448,40 +3448,40 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3493,40 +3493,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3538,40 +3538,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 28</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3583,102 +3583,102 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-gartner-it.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-signet-jewelers-sig.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -3686,27 +3686,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3718,40 +3718,40 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3763,40 +3763,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 36</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cognex-cgnx.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3808,40 +3808,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3853,40 +3853,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3898,40 +3898,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▼ 49</t>
+          <t>▲ 24</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-axe-compute-agpu.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3943,40 +3943,40 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3988,40 +3988,40 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 49</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4033,130 +4033,130 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4168,40 +4168,40 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4213,85 +4213,85 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>GATX</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4303,40 +4303,40 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4348,40 +4348,40 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4393,130 +4393,130 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 28</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>GATX</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-gatx-gatx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4528,40 +4528,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4573,97 +4573,97 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▲ 21</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>UROY</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>SZKMY</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4672,31 +4672,31 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4708,40 +4708,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4753,40 +4753,40 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-suzuki-motor-adr-szkmy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4798,40 +4798,40 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▲ 27</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4843,40 +4843,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4888,40 +4888,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4933,40 +4933,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4978,40 +4978,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 33</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-dxp-enterprises-dxpe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5023,130 +5023,130 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 34</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5163,35 +5163,35 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5203,16 +5203,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -5221,22 +5221,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5248,12 +5248,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -5261,48 +5261,48 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmarket-neu.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -5338,40 +5338,40 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-methanex-meoh.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5383,40 +5383,40 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▼ 26</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5428,40 +5428,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5473,40 +5473,40 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5518,40 +5518,40 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5563,16 +5563,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -5596,97 +5596,97 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-american-states-water-awr.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5703,35 +5703,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5748,40 +5748,40 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>CSTM</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-constellium-cl-a-cstm.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5793,35 +5793,35 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5838,35 +5838,35 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5883,11 +5883,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -5896,22 +5896,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5923,40 +5923,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5968,40 +5968,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6013,40 +6013,40 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-pampa-energia-adr-pam.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6058,16 +6058,16 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 33</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -6076,22 +6076,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6103,7 +6103,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6112,31 +6112,31 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6148,40 +6148,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6193,40 +6193,40 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 37</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6238,40 +6238,40 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6283,40 +6283,40 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6328,40 +6328,40 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6373,40 +6373,40 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6418,16 +6418,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
+          <t>EAT</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
           <t>LKNCY</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-luckin-coffee-adr-lkncy.htm</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>EAT</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6463,40 +6463,40 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6508,16 +6508,16 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -6553,16 +6553,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -6571,22 +6571,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6598,7 +6598,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6607,31 +6607,31 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6643,16 +6643,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -6688,40 +6688,40 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6733,40 +6733,40 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6778,40 +6778,40 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6823,45 +6823,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>142</v>
+        <v>52</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>대기</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -478,40 +478,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 98</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>busins svc</t>
-        </is>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -523,7 +519,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -532,31 +528,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,7 +564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,43 +573,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,31 +618,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -658,12 +654,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -671,27 +667,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -703,40 +699,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,40 +744,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -793,40 +789,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -838,40 +834,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -883,57 +879,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -941,39 +937,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-salesforce-crm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -982,31 +978,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1018,85 +1014,85 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palantir-technologies-pltr.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1108,40 +1104,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1153,85 +1149,85 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-iovance-biotherapeutics-iova.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1243,85 +1239,85 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>VBNK</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1333,40 +1329,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1378,7 +1374,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1387,31 +1383,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1423,40 +1419,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▲ 39</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1468,175 +1464,175 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CBWTF</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VBNK</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-natwest-group-adr-nwg.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>SUTNY</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cocacola-consolidated-coke.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1648,40 +1644,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>PGEN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-berkshire-hathaway-cl-b-brk.b.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-precigen-pgen.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1693,40 +1689,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SUTNY</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-sumitomo-mitsui-trust-group-adr-sutny.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-semtech-smtc.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SUTNY</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1738,106 +1734,106 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▼ 21</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1846,22 +1842,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1873,85 +1869,85 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palomar-holdings-plmr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BGC</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-bgc-group-cl-a-bgc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-dorchester-minerals-dmlp.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1963,16 +1959,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1986,38 +1982,38 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>APH</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>AVT</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>AVT</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2026,112 +2022,112 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>BGC</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>PLMR</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2143,40 +2139,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cocacola-consolidated-coke.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2188,175 +2184,175 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-semtech-smtc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CAC</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 26</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2368,40 +2364,38 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▼ 5</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>38</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2413,40 +2407,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 46</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2458,40 +2452,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 30</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2503,40 +2497,40 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2548,16 +2542,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 27</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2581,12 +2575,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CGNX</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2598,35 +2592,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2643,40 +2637,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▲ 38</t>
+          <t>▲ 33</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2688,35 +2682,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2733,35 +2727,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2778,80 +2772,80 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 17</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ACVA</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2863,12 +2857,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2876,27 +2870,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TTNDY</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-techtronic-industries-adr-ttndy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>TTNDY</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2908,40 +2902,40 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2953,40 +2947,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 20</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2998,40 +2992,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3043,40 +3037,40 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3088,40 +3082,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3133,40 +3127,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3178,40 +3172,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3223,40 +3217,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-signet-jewelers-sig.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3268,40 +3262,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-science-applications-international-saic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3313,40 +3307,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 20</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3358,130 +3352,130 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▲ 17</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>MKTAY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-makita-adr-mktay.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>TTNDY</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 31</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3493,40 +3487,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3538,40 +3532,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▼ 28</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3583,85 +3577,85 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-gartner-it.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-signet-jewelers-sig.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3678,35 +3672,35 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 27</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3723,35 +3717,35 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3768,35 +3762,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▼ 36</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3813,35 +3807,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3858,35 +3852,35 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3903,35 +3897,35 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▲ 24</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3948,40 +3942,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3993,11 +3987,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▼ 49</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4038,35 +4032,35 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4083,40 +4077,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-gartner-it.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4128,35 +4122,35 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 29</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,27 +4175,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4218,40 +4212,40 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>GATX</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4263,35 +4257,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4308,35 +4302,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4353,35 +4347,35 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4398,40 +4392,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▼ 28</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>AGPU</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4443,35 +4437,35 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▼ 28</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4488,35 +4482,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4533,35 +4527,35 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4578,35 +4572,35 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4631,32 +4625,32 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>SZKMY</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4668,35 +4662,35 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4713,35 +4707,35 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4758,35 +4752,35 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-box-cl-a-box.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4803,35 +4797,35 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4848,35 +4842,35 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4888,40 +4882,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4933,40 +4927,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4978,40 +4972,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5023,85 +5017,85 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 23</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5113,40 +5107,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5158,40 +5152,40 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5203,40 +5197,40 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5248,85 +5242,85 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmarket-neu.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5338,85 +5332,85 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 20</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5428,85 +5422,85 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5518,40 +5512,40 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5563,40 +5557,40 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-bill-holdings-bill.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5608,85 +5602,85 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-american-states-water-awr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>PAM</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5698,40 +5692,40 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>CSTM</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-constellium-cl-a-cstm.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>CSTM</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5743,85 +5737,85 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CSTM</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-constellium-cl-a-cstm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5833,85 +5827,85 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-target-hospitality-th.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5923,40 +5917,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5968,40 +5962,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6013,85 +6007,85 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6108,35 +6102,35 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6148,40 +6142,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6198,35 +6192,35 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▼ 37</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6243,40 +6237,40 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -6288,35 +6282,35 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6333,35 +6327,35 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6378,35 +6372,35 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6423,40 +6417,40 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>LKNCY</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6468,35 +6462,35 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6513,11 +6507,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -6526,22 +6520,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6558,35 +6552,35 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6603,35 +6597,35 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6648,35 +6642,35 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6693,35 +6687,35 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6738,11 +6732,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -6778,45 +6772,45 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>대기</t>
         </is>
       </c>
     </row>
@@ -6832,7 +6826,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -6856,7 +6850,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -478,36 +478,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>▲ 98</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>98</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -519,12 +523,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -564,40 +568,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -609,40 +613,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -654,40 +658,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -699,12 +703,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -712,27 +716,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -744,40 +748,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -789,85 +793,85 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-crowdstrike-holdings-crwd.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -879,85 +883,85 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -969,40 +973,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palantir-technologies-pltr.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1014,57 +1018,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 30</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palantir-technologies-pltr.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1072,27 +1076,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Medical - Revenue Biotech</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1104,40 +1108,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1149,40 +1153,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1194,102 +1198,102 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>VBNK</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1297,27 +1301,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1329,40 +1333,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1374,16 +1378,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1419,61 +1423,61 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>VBNK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1509,7 +1513,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1518,31 +1522,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1554,16 +1558,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1587,52 +1591,52 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SUTNY</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1644,16 +1648,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1662,67 +1666,67 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PGEN</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-precigen-pgen.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-semtech-smtc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1734,85 +1738,85 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1824,7 +1828,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1833,31 +1837,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1869,40 +1873,40 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1914,175 +1918,175 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-dorchester-minerals-dmlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BGC</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>PGEN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2094,12 +2098,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2107,27 +2111,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>PLMR</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2139,16 +2143,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2162,62 +2166,62 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>AKO.B</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>COKE</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cocacola-consolidated-coke.htm</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>COKE</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2229,40 +2233,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2274,40 +2278,40 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2319,40 +2323,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 26</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2364,38 +2368,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>▲ 2</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>45</v>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2407,40 +2413,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▲ 46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2452,40 +2458,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 30</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2497,40 +2503,40 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2542,40 +2548,40 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2592,35 +2598,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2637,35 +2643,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▲ 33</t>
+          <t>▲ 25</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>YAHOY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2682,35 +2688,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2727,40 +2733,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>KAOOY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-kao-adr-kaooy.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2772,35 +2778,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 17</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2817,35 +2823,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2862,35 +2868,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2902,40 +2908,38 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▼ 7</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>48</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2952,40 +2956,40 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>CFFN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-capitol-federal-financial-cffn.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2997,40 +3001,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3042,35 +3046,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3087,35 +3091,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3132,35 +3136,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 26</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3177,80 +3181,80 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>MKTAY</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-signet-jewelers-sig.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3262,40 +3266,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3307,40 +3311,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 20</t>
+          <t>▲ 28</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3352,130 +3356,130 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MKTAY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-makita-adr-mktay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>TTNDY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▲ 31</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3487,85 +3491,85 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>EJPRY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-east-japan-railway-adr-ejpry.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3577,40 +3581,40 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3622,7 +3626,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3631,36 +3635,36 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3672,35 +3676,35 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3717,35 +3721,35 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-ly-adr-yahoy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3762,35 +3766,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 22</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3807,40 +3811,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3852,35 +3856,35 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3897,35 +3901,33 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▲ 16</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>94</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3942,11 +3944,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3970,12 +3972,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3987,40 +3989,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 23</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4032,35 +4034,35 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4077,35 +4079,35 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-gartner-it.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4122,35 +4124,35 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 29</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4167,35 +4169,35 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4212,35 +4214,35 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4257,35 +4259,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 35</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4302,35 +4304,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4347,35 +4349,35 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4392,35 +4394,35 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▼ 28</t>
+          <t>▼ 22</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4432,40 +4434,40 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4477,40 +4479,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4522,40 +4524,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4567,40 +4569,40 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4612,12 +4614,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4625,27 +4627,27 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4657,40 +4659,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4702,61 +4704,61 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -4770,62 +4772,62 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>TRVG</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
           <t>EXPE</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>EXPE</t>
-        </is>
-      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4837,40 +4839,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4887,35 +4889,35 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4932,35 +4934,35 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4977,35 +4979,35 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-orion-energy-systems-oesx.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5022,35 +5024,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 23</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5067,35 +5069,35 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5112,40 +5114,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5157,35 +5159,35 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5202,35 +5204,35 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5242,40 +5244,40 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5287,7 +5289,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5296,31 +5298,31 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5332,12 +5334,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -5345,48 +5347,48 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▼ 20</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -5395,22 +5397,22 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5422,40 +5424,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>CSTM</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5472,35 +5474,35 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5517,35 +5519,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5562,35 +5564,35 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5607,11 +5609,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -5652,35 +5654,35 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5697,35 +5699,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CSTM</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-constellium-cl-a-cstm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>CSTM</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5737,45 +5739,45 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>NPK</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5787,35 +5789,35 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-national-presto-industries-npk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5827,45 +5829,45 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-target-hospitality-th.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5877,35 +5879,35 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5922,35 +5924,35 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5967,35 +5969,35 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6012,40 +6014,40 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6057,35 +6059,35 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6102,35 +6104,35 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6142,40 +6144,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6187,130 +6189,130 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-bill-holdings-bill.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6327,35 +6329,35 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6372,40 +6374,40 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>LKNCY</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-luckin-coffee-adr-lkncy.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -6417,35 +6419,35 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6457,40 +6459,40 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6507,35 +6509,35 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6547,40 +6549,40 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6597,35 +6599,35 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6642,11 +6644,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -6687,11 +6689,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -6781,7 +6783,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -6805,7 +6807,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6826,7 +6828,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -6850,7 +6852,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,11 +483,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -528,11 +528,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -573,11 +573,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -618,11 +618,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -663,11 +663,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -708,11 +708,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -798,11 +798,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -826,12 +826,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -933,11 +933,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1023,11 +1023,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▲ 30</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1063,40 +1063,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medical - Revenue Biotech</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1117,31 +1117,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1153,40 +1153,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1198,85 +1198,85 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1288,40 +1288,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1333,40 +1333,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1378,40 +1378,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1423,16 +1423,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1456,52 +1456,52 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VBNK</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1513,40 +1513,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-natwest-group-adr-nwg.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1558,40 +1558,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-natwest-group-adr-nwg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1603,16 +1603,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1653,11 +1653,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1666,22 +1666,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1743,11 +1743,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1788,11 +1788,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1833,11 +1833,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1878,35 +1878,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1923,35 +1923,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1968,35 +1968,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2013,35 +2013,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PGEN</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2103,40 +2103,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2156,72 +2156,72 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2233,40 +2233,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2278,40 +2278,40 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2323,40 +2323,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2368,40 +2368,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2422,31 +2422,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2458,40 +2458,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2503,16 +2503,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2548,40 +2548,40 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2593,12 +2593,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2606,27 +2606,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2638,85 +2638,85 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▲ 25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>YAHOY</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2728,85 +2728,85 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KAOOY</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-kao-adr-kaooy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2818,16 +2818,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2863,40 +2863,40 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2908,38 +2908,40 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>56</v>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>CFFN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-capitol-federal-financial-cffn.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>CFFN</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2951,130 +2953,130 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CFFN</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-capitol-federal-financial-cffn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3086,40 +3088,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3131,40 +3133,38 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▲ 26</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>86</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3176,45 +3176,45 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MKTAY</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3226,35 +3226,35 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3271,35 +3271,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3316,35 +3316,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▲ 28</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3406,35 +3406,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3451,40 +3451,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>EJPRY</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3496,40 +3496,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>EJPRY</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-east-japan-railway-adr-ejpry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3541,35 +3541,35 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3586,35 +3586,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3631,35 +3631,35 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3676,35 +3676,35 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3721,35 +3721,35 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3766,35 +3766,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▼ 22</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3811,11 +3811,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -3856,35 +3856,35 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 26</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>KAOOY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-kao-adr-kaooy.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>KAOOY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3901,10 +3901,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>78</v>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>busins svc</t>
@@ -3989,11 +3991,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▲ 23</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4017,12 +4019,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4034,11 +4036,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4079,11 +4081,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -4124,35 +4126,35 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4169,35 +4171,35 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4214,35 +4216,35 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4259,11 +4261,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▼ 35</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -4304,35 +4306,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4349,11 +4351,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4394,11 +4396,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▼ 22</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4434,40 +4436,38 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▲ 4</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>95</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4479,40 +4479,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4524,40 +4524,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4569,16 +4569,16 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -4587,22 +4587,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4614,40 +4614,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4659,40 +4659,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4704,52 +4704,52 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4758,76 +4758,76 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4839,40 +4839,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4884,40 +4884,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4929,40 +4929,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4974,40 +4974,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5019,40 +5019,40 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5064,40 +5064,40 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5109,16 +5109,16 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -5142,52 +5142,52 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5199,40 +5199,40 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5244,40 +5244,40 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5289,40 +5289,40 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5334,40 +5334,40 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5379,40 +5379,40 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5424,85 +5424,85 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CSTM</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5514,40 +5514,40 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5559,16 +5559,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -5604,40 +5604,40 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5649,40 +5649,40 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5694,40 +5694,40 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5739,85 +5739,85 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>NPK</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5829,40 +5829,40 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5874,40 +5874,40 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5919,16 +5919,16 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -5964,40 +5964,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6009,16 +6009,16 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -6059,11 +6059,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -6104,11 +6104,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -6144,40 +6144,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6189,16 +6189,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -6222,28 +6222,28 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -6279,16 +6279,16 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -6329,11 +6329,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -6374,11 +6374,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -6402,12 +6402,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>LKNCY</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6419,11 +6419,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -6459,16 +6459,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -6509,11 +6509,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -6549,40 +6549,40 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6599,35 +6599,35 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6774,45 +6774,45 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -1383,11 +1383,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1428,11 +1428,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1563,11 +1563,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1608,11 +1608,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1653,11 +1653,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2013,11 +2013,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2103,11 +2103,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2148,11 +2148,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2188,40 +2188,38 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>40</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2233,7 +2231,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2242,31 +2240,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2278,7 +2276,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2287,31 +2285,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2323,7 +2321,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2332,31 +2330,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2368,7 +2366,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2377,31 +2375,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2413,7 +2411,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2422,31 +2420,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2458,40 +2456,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2503,12 +2501,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2516,27 +2514,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2548,7 +2546,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2557,31 +2555,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2593,7 +2591,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2602,31 +2600,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2638,7 +2636,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2647,31 +2645,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2683,40 +2681,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2728,40 +2726,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2773,40 +2771,40 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2818,7 +2816,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2827,31 +2825,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2863,40 +2861,40 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2908,7 +2906,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2917,31 +2915,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CFFN</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-capitol-federal-financial-cffn.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>CFFN</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2953,7 +2951,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2962,31 +2960,31 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>CFFN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-capitol-federal-financial-cffn.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>CFFN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2998,40 +2996,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3043,7 +3041,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3052,31 +3050,31 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3088,40 +3086,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3133,38 +3131,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>60</v>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3176,40 +3176,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3221,40 +3221,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3266,40 +3266,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3311,40 +3311,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3365,31 +3365,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3401,40 +3401,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3446,85 +3446,85 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>EJPRY</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3536,40 +3536,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3581,40 +3581,40 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3626,40 +3626,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3671,40 +3671,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3716,40 +3716,40 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3761,40 +3761,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3806,7 +3806,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3815,31 +3815,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3851,40 +3851,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▼ 26</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAOOY</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-kao-adr-kaooy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>KAOOY</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3896,7 +3896,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3905,31 +3905,31 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>KAOOY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-kao-adr-kaooy.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>KAOOY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3941,7 +3941,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3959,22 +3959,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3986,7 +3986,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3995,31 +3995,31 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,7 +4031,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4040,31 +4040,31 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4076,7 +4076,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4085,31 +4085,31 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4121,40 +4121,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4171,11 +4171,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -4216,11 +4216,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -4306,11 +4306,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -4441,10 +4441,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>90</v>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>energy</t>
@@ -4664,11 +4666,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -4709,11 +4711,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -4754,11 +4756,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -4799,11 +4801,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -4889,11 +4891,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -4934,11 +4936,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -4979,11 +4981,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -5114,11 +5116,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -5159,11 +5161,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -5249,11 +5251,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -5519,11 +5521,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -5564,11 +5566,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -5609,11 +5611,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -5654,11 +5656,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -5699,11 +5701,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -5924,11 +5926,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -5969,11 +5971,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -6014,11 +6016,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -6149,11 +6151,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -6194,11 +6196,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -6239,11 +6241,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -6284,11 +6286,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -6464,11 +6466,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -6554,11 +6556,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -6779,11 +6781,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -6828,7 +6830,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -6852,7 +6854,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,35 +483,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valero-energy-vlo.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -528,40 +528,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -573,35 +573,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,35 +618,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -663,40 +663,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marathon-petroleum-mpc.htm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -708,35 +708,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -753,40 +753,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -798,35 +798,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-crowdstrike-holdings-crwd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -843,35 +843,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -888,35 +888,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -933,35 +933,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -973,16 +973,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -991,22 +991,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palantir-technologies-pltr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1018,40 +1018,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1113,35 +1113,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1171,27 +1171,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,35 +1248,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,35 +1293,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1383,35 +1383,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>VBNK</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>VBNK</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1473,35 +1473,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1518,35 +1518,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-natwest-group-adr-nwg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1563,35 +1563,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-natwest-group-adr-nwg.htm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1608,35 +1608,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-telix-pharmaceuticals-adr-tlx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1648,40 +1648,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-incyte-incy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1693,61 +1693,61 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>TLX</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1756,22 +1756,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1783,7 +1783,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1792,31 +1792,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1828,40 +1828,40 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1873,16 +1873,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1891,22 +1891,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1918,40 +1918,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1963,85 +1963,85 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 27</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>META</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2053,40 +2053,40 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2098,40 +2098,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2143,40 +2143,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2188,15 +2188,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>▼ 1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>39</v>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>misc</t>
@@ -2231,40 +2233,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2276,40 +2278,40 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2321,40 +2323,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 28</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2366,40 +2368,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2411,40 +2413,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2456,85 +2458,85 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>INFU</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-infusystem-holdings-infu.htm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2546,85 +2548,85 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2636,40 +2638,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2681,40 +2683,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 27</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2726,40 +2728,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2771,16 +2773,16 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2789,22 +2791,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2816,40 +2818,40 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2861,40 +2863,40 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2906,61 +2908,61 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>TTNDY</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-techtronic-industries-adr-ttndy.htm</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2969,22 +2971,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CFFN</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-capitol-federal-financial-cffn.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CFFN</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2996,40 +2998,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 21</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3041,40 +3043,40 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3086,40 +3088,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3131,40 +3133,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3176,40 +3178,40 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>CFFN</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-capitol-federal-financial-cffn.htm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>CFFN</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3221,40 +3223,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 28</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-match-group-mtch.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3266,85 +3268,85 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 27</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3356,40 +3358,40 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3401,40 +3403,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3446,16 +3448,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3464,67 +3466,67 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>ESTC</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elastic-estc.htm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3536,40 +3538,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3581,40 +3583,40 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 21</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3626,40 +3628,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 26</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3671,40 +3673,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3716,40 +3718,40 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3761,12 +3763,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -3806,40 +3808,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3851,40 +3853,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3896,40 +3898,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KAOOY</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-kao-adr-kaooy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>KAOOY</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3941,40 +3943,40 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 26</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3986,16 +3988,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4004,22 +4006,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,85 +4033,85 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-nvent-electric-nvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>KAOOY</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4121,45 +4123,45 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>GATX</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-gatx-gatx.htm</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4171,35 +4173,35 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4216,35 +4218,35 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4261,35 +4263,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4301,40 +4303,40 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4346,40 +4348,40 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4391,7 +4393,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4400,31 +4402,31 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4436,40 +4438,40 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4486,35 +4488,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4531,35 +4533,35 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4576,35 +4578,35 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4616,40 +4618,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4661,40 +4663,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4706,40 +4708,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4751,40 +4753,40 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4801,35 +4803,35 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4841,40 +4843,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4891,35 +4893,35 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4936,35 +4938,35 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4981,35 +4983,35 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5026,35 +5028,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5071,35 +5073,35 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5116,35 +5118,33 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>105</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-h-world-group-adr-htht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5161,40 +5161,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>ATAT</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atour-lifestyle-holdings-adr-atat.htm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>HTHT</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5206,35 +5206,35 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5251,35 +5251,35 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5296,35 +5296,35 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5341,35 +5341,35 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5386,35 +5386,35 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5431,35 +5431,35 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5476,35 +5476,35 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5521,35 +5521,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5566,35 +5566,35 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5611,35 +5611,35 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5656,40 +5656,40 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 20</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5701,35 +5701,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5746,40 +5746,40 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>IRS</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5791,35 +5791,35 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5836,35 +5836,35 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5881,35 +5881,35 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5926,35 +5926,35 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6061,35 +6061,35 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6106,35 +6106,35 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-irsainversiones-y-representaciones-gdr-irs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6196,35 +6196,35 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-bill-holdings-bill.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6241,35 +6241,35 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6286,35 +6286,35 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-bill-holdings-bill.htm</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6331,35 +6331,35 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6376,35 +6376,35 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LKNCY</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-luckin-coffee-adr-lkncy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>LKNCY</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6421,35 +6421,35 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6466,35 +6466,35 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>LKNCY</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-luckin-coffee-adr-lkncy.htm</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>LKNCY</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6556,35 +6556,35 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6601,35 +6601,35 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6646,35 +6646,35 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6691,35 +6691,35 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6736,35 +6736,35 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6781,35 +6781,35 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -491,27 +491,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -528,40 +528,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -573,35 +573,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,35 +618,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dell-technologies-cl-c-dell.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -663,35 +663,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marathon-petroleum-mpc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-netapp-ntap.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -708,35 +708,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -753,11 +753,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -776,17 +776,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -798,40 +798,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>UGP</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ultrapar-participacoes-adr-ugp.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -843,35 +843,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -888,11 +888,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -906,22 +906,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>CDNA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm?symbolType=stock&amp;countryCode=us</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>DGX</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quest-diagnostics-dgx.htm</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -933,35 +933,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-frontline-fro.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,40 +1023,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1068,35 +1068,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1113,35 +1113,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1158,40 +1158,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1203,40 +1203,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-okeanis-eco-tankers-eco.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1248,80 +1248,80 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-daiwa-securities-group-adr-dseey.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dorian-lpg-lpg.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▲ 21</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1333,40 +1333,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 23</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-avnet-avt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1423,85 +1423,85 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ing-groep-adr-ing.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>VBNK</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1513,40 +1513,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1558,85 +1558,83 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>▼ 1</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>25</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-natwest-group-adr-nwg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1648,85 +1646,85 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>VBNK</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-petroleo-brasileiro-adr-pbr.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>TLX</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1738,40 +1736,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1783,40 +1781,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1828,40 +1826,40 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1873,40 +1871,40 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 24</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1918,40 +1916,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1963,40 +1961,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 27</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fastenal-fast.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2008,130 +2006,130 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>INFU</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xp-xp.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>DSEEY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2143,40 +2141,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2188,40 +2186,40 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2233,130 +2231,130 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>TTNDY</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>NWG</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 28</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2368,40 +2366,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 30</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2413,57 +2411,57 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 23</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tenet-healthcare-thc.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2471,72 +2469,72 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>INFU</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-infusystem-holdings-infu.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▼ 21</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-news-corp-cl-a-nwsa.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2548,85 +2546,85 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 30</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-sei-investments-seic.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ulta-beauty-ulta.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2638,40 +2636,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-msandad-insurance-group-holdings-adr-msady.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2683,40 +2681,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>▲ 41</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-equinor-adr-eqnr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2728,40 +2726,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2773,40 +2771,40 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2818,57 +2816,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fox-corp-cl-a-foxa.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2876,39 +2874,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-hewlett-packard-enterprise-hpe.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2917,31 +2915,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TTNDY</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-techtronic-industries-adr-ttndy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2953,40 +2951,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-farmers-and-merchants-bancorp-fmao.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2998,40 +2996,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▼ 21</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3043,85 +3041,85 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>ITT</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-itt-itt.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3133,40 +3131,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3178,16 +3176,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3201,62 +3199,62 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>GCBC</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm?symbolType=stock&amp;countryCode=us</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>CFFN</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-capitol-federal-financial-cffn.htm</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>CFFN</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▲ 28</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3268,16 +3266,16 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3296,57 +3294,57 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3358,7 +3356,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3367,31 +3365,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>GATX</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-gatx-gatx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>GATX</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3403,40 +3401,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 33</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>META</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>META</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3448,40 +3446,40 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ESTC</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elastic-estc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-nasdaq-ndaq.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3493,85 +3491,85 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>ESTC</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3583,102 +3581,102 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 21</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-sb-financial-group-sbfg.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▼ 26</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ptc-ptc.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -3686,27 +3684,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3718,85 +3716,85 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>SPNT</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-siriuspoint-spnt.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>MSADY</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3808,16 +3806,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3826,22 +3824,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3853,40 +3851,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▼ 24</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3898,40 +3896,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 19</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3943,40 +3941,40 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▼ 26</t>
+          <t>▼ 38</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3988,130 +3986,130 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 33</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>KAOOY</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4123,85 +4121,85 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>GATX</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-gatx-gatx.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4213,16 +4211,16 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -4231,22 +4229,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4258,40 +4256,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4303,40 +4301,40 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▲ 21</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-autodesk-adsk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>WHD</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4348,40 +4346,40 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4393,40 +4391,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-andersons-ande.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4438,61 +4436,61 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-marriott-international-mar.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>ATAT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4511,7 +4509,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4528,40 +4526,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4573,40 +4571,40 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4618,40 +4616,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4663,40 +4661,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4708,40 +4706,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 30</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4753,40 +4751,40 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4798,40 +4796,40 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4843,40 +4841,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4888,40 +4886,40 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4933,40 +4931,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4978,40 +4976,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5023,40 +5021,40 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5068,83 +5066,85 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>ANDE</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>▼ 13</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>93</v>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5161,40 +5161,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ATAT</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atour-lifestyle-holdings-adr-atat.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>HTHT</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -5206,35 +5206,35 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5246,40 +5246,40 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5291,16 +5291,16 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -5309,22 +5309,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5336,40 +5336,40 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5381,12 +5381,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -5394,27 +5394,27 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5426,40 +5426,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5471,40 +5471,40 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5516,40 +5516,40 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5561,61 +5561,61 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>AIRT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5651,85 +5651,85 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▼ 20</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-air-t-airt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5741,40 +5741,40 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>CSTM</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-constellium-cl-a-cstm.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5786,40 +5786,40 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5844,27 +5844,27 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5876,40 +5876,40 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5921,40 +5921,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5966,85 +5966,85 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-st-joe-joe.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 39</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6056,40 +6056,40 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6101,7 +6101,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6146,40 +6146,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6191,16 +6191,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6236,40 +6236,40 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6281,40 +6281,40 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 32</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-bill-holdings-bill.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -6339,72 +6339,72 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6416,40 +6416,40 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6461,16 +6461,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -6484,34 +6484,34 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
+          <t>EAT</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm?symbolType=stock&amp;countryCode=us</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
           <t>LKNCY</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-luckin-coffee-adr-lkncy.htm</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>LKNCY</t>
-        </is>
-      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6551,7 +6551,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6560,31 +6560,31 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6596,16 +6596,16 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -6614,22 +6614,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6641,12 +6641,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -6654,27 +6654,27 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6686,7 +6686,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm</t>
+          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6731,7 +6731,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6776,45 +6776,45 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>대기</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,35 +483,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -528,35 +528,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -573,35 +573,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,35 +618,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -663,40 +663,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-netapp-ntap.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -708,35 +708,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>UGP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ultrapar-participacoes-adr-ugp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>UGP</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -753,35 +753,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -806,27 +806,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UGP</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ultrapar-participacoes-adr-ugp.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-everpure-p.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -843,35 +843,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -888,35 +888,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -928,40 +928,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -978,40 +978,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1023,11 +1023,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1041,17 +1041,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm?symbolType=stock&amp;countryCode=us</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>QRVO</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-qorvo-qrvo.htm?symbolType=stock&amp;countryCode=us</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>TSM</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1068,35 +1068,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1113,35 +1113,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hamilton-beach-brands-holding-cl-a-hbb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-okeanis-eco-tankers-eco.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1203,40 +1203,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-okeanis-eco-tankers-eco.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1248,80 +1248,80 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dorian-lpg-lpg.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1333,40 +1333,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▲ 23</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1383,35 +1383,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1428,40 +1428,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▼ 4</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>20</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1473,35 +1471,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1518,11 +1516,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1558,15 +1556,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>26</v>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>medical</t>
@@ -1584,57 +1584,57 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1646,16 +1646,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1674,57 +1674,57 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VBNK</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▲ 21</t>
+          <t>▲ 40</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-petroleo-brasileiro-adr-pbr.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1736,40 +1736,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-itochu-adr-itocy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-petroleo-brasileiro-adr-pbr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1781,40 +1781,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1826,16 +1826,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1871,40 +1871,40 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 24</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-b-adr-ako.b.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1916,40 +1916,40 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1961,16 +1961,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1989,147 +1989,145 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-fastenal-fast.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fastenal-fast.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 17</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>INFU</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▼ 19</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>19</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xp-xp.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DSEEY</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2141,175 +2139,175 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>AKO.B</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-johnson-controls-international-jci.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>ITOCY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>TTNDY</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>REPYY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-repsol-adr-repyy.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>KGEI</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2321,40 +2319,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 25</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>META</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>META</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2371,35 +2369,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▲ 30</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2416,40 +2414,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▲ 23</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tenet-healthcare-thc.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xp-xp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2461,11 +2459,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2506,35 +2504,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▼ 21</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2551,35 +2549,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 30</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2591,85 +2589,85 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>ICAGY</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-kolibri-global-energy-kgei.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-international-consolidated-airlines-group-adr-icagy.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2681,40 +2679,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▲ 41</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2726,40 +2724,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2771,40 +2769,40 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 34</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xometry-xmtr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2816,175 +2814,175 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-fox-corp-cl-a-foxa.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-hewlett-packard-enterprise-hpe.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>ITT</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-itt-itt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>ITT</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2996,106 +2994,106 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 22</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ITT</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-itt-itt.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3131,40 +3129,40 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3176,61 +3174,61 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 20</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CFFN</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3239,22 +3237,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3266,40 +3264,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3311,40 +3309,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SPNT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-siriuspoint-spnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>SPNT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3356,85 +3354,85 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▼ 23</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>GATX</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-gatx-gatx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>GATX</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3446,130 +3444,130 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-nasdaq-ndaq.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ESTC</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3581,130 +3579,130 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-sb-financial-group-sbfg.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ptc-ptc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>FMAO</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ptc-ptc.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-haemonetics-hae.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3716,85 +3714,85 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SPNT</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-siriuspoint-spnt.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>MSADY</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3806,40 +3804,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3851,40 +3849,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▼ 24</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3896,16 +3894,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▼ 19</t>
+          <t>▼ 14</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3914,22 +3912,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>GATX</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-gatx-gatx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>GATX</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3941,40 +3939,40 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▼ 38</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3986,16 +3984,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▼ 33</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4014,57 +4012,57 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4076,40 +4074,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-marriott-international-mar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4121,16 +4119,16 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4139,22 +4137,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4166,85 +4164,85 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▲ 16</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4256,16 +4254,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -4301,16 +4299,16 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -4324,38 +4322,38 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
+          <t>FTI</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm?symbolType=stock&amp;countryCode=us</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
           <t>WHD</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cactus-cl-a-whd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>WHD</t>
-        </is>
-      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4364,22 +4362,22 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4391,40 +4389,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4436,7 +4434,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4445,76 +4443,76 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-marriott-international-mar.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ATAT</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4526,85 +4524,85 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmarket-neu.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-factset-research-systems-fds.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4616,40 +4614,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4661,40 +4659,40 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4706,40 +4704,40 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 30</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4751,12 +4749,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -4764,27 +4762,27 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4796,40 +4794,40 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-flotek-industries-ftk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4841,40 +4839,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4886,85 +4884,85 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 34</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>ESTC</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elastic-estc.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4976,12 +4974,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -4989,27 +4987,27 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5021,16 +5019,16 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -5066,85 +5064,85 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ANDE</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▼ 13</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5156,40 +5154,40 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5201,40 +5199,40 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5246,40 +5244,40 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5291,61 +5289,61 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>CSTM</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -5354,22 +5352,22 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5381,40 +5379,40 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5426,40 +5424,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5471,85 +5469,85 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-flexsteel-industries-flxs.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5561,85 +5559,85 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>AIRT</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5651,40 +5649,40 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5696,16 +5694,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -5714,22 +5712,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5741,7 +5739,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5750,121 +5748,121 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CSTM</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-constellium-cl-a-cstm.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5876,40 +5874,40 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5921,40 +5919,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5966,85 +5964,85 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-st-joe-joe.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▼ 39</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6056,40 +6054,40 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6101,16 +6099,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -6146,16 +6144,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -6191,40 +6189,40 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6236,85 +6234,85 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>WEYS</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-weyco-group-weys.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>JRSH</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▼ 32</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6326,16 +6324,16 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -6354,57 +6352,57 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6416,16 +6414,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -6434,22 +6432,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6461,61 +6459,61 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>LKNCY</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -6551,57 +6549,57 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>SHLS</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-shoals-technologies-group-shls.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -6609,27 +6607,27 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6641,135 +6639,135 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>대기</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-jerash-holdings-us-jrsh.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>대기</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>대기</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6783,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -6809,7 +6807,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6830,7 +6828,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -6854,12 +6852,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>에러 발생</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,35 +483,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -536,27 +536,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -573,35 +573,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,40 +618,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-super-micro-computer-smci.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>P</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -663,35 +663,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -708,35 +708,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UGP</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ultrapar-participacoes-adr-ugp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>UGP</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -753,35 +753,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Consumer Prod-Electronic</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -798,35 +798,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-everpure-p.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marathon-petroleum-mpc.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>UGP</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -843,35 +843,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -883,16 +883,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,27 +901,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Consumer Prod-Electronic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-garmin-grmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -933,35 +933,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -978,40 +978,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1046,17 +1046,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Elec-Semicondctor Fablss</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-okeanis-eco-tankers-eco.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-nvidia-nvda.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1158,35 +1158,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elec-Semicondctor Fablss</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-advanced-micro-devices-amd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-okeanis-eco-tankers-eco.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,35 +1248,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,35 +1293,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>▼ 11</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>9</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1338,80 +1336,80 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-williamssonoma-wsm.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-best-buy-bby.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1423,59 +1421,61 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>▲ 5</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>28</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>VBNK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>AVT</t>
+          <t>VBNK</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1484,22 +1484,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1511,16 +1511,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1574,22 +1574,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1601,40 +1601,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1646,16 +1646,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1664,22 +1664,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VBNK</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>VBNK</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1691,85 +1691,85 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▲ 40</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Elec-Semiconductor Equip</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corpay-cpay.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>ATEYY</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-petroleo-brasileiro-adr-pbr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1781,40 +1781,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1826,40 +1826,40 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 33</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1871,85 +1871,85 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>ICAGY</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1961,40 +1961,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-fastenal-fast.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2006,40 +2006,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 17</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-johnson-controls-international-jci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2056,33 +2056,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>▼ 5</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>32</v>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Equip</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-advantest-adr-ateyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ATEYY</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2099,35 +2101,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2144,40 +2146,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>AKO.B</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2189,35 +2191,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-johnson-controls-international-jci.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-nasdaq-ndaq.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ITOCY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2234,35 +2236,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2279,40 +2281,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>▲ 8</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>50</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>REPYY</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-repsol-adr-repyy.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fox-corp-cl-a-foxa.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KGEI</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -2324,35 +2324,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 25</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2364,40 +2364,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2409,40 +2409,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 24</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xp-xp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2454,12 +2454,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2499,40 +2499,40 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xp-xp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2544,16 +2544,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2589,40 +2589,38 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>51</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ICAGY</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-international-consolidated-airlines-group-adr-icagy.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-celestica-cls.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2634,40 +2632,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2679,40 +2677,38 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▼ 13</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>41</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-sb-financial-group-sbfg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2724,40 +2720,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2769,40 +2765,40 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 34</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2814,85 +2810,85 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 24</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-union-pacific-unp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-shell-adr-shel.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>PBR</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmont-nem.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2904,85 +2900,85 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ITT</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-itt-itt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ITT</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2994,40 +2990,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>ITT</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3039,40 +3035,40 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▼ 24</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fastenal-fast.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3084,40 +3080,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>META</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>META</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3129,61 +3125,61 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>GATX</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▼ 20</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3219,40 +3215,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3264,40 +3260,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3309,40 +3305,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SPNT</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-siriuspoint-spnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SPNT</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3354,85 +3350,85 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▼ 23</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>THC</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>SPNT</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-siriuspoint-spnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>SPNT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3444,40 +3440,40 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3489,85 +3485,85 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>▼ 12</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>CNI</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-canadian-national-railway-cni.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3579,40 +3575,40 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ptc-ptc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3624,40 +3620,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3669,40 +3665,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3714,7 +3710,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3723,31 +3719,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3759,40 +3755,40 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>▲ 15</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3804,40 +3800,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 34</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>REPYY</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-repsol-adr-repyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>REPYY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3849,40 +3845,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3894,40 +3890,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▼ 14</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>GATX</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-gatx-gatx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>GATX</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3939,12 +3935,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -3952,27 +3948,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-marriott-international-mar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3984,40 +3980,40 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 18</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4029,40 +4025,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4074,40 +4070,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-marriott-international-mar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4119,40 +4115,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▲ 20</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4164,130 +4160,128 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>▲ 8</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>97</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4299,85 +4293,85 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>WHD</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4389,40 +4383,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▲ 13</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4434,40 +4428,40 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4479,7 +4473,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4488,31 +4482,31 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ptc-ptc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4524,85 +4518,85 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 25</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmarket-neu.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-flexsteel-industries-flxs.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>92</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 36</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4614,40 +4608,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>93</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4659,16 +4653,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>94</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -4677,22 +4671,22 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-corecivic-cxw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4704,12 +4698,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4717,27 +4711,27 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4749,61 +4743,61 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jakks-pacific-jakk.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>ESCA</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -4812,22 +4806,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4839,40 +4833,40 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>98</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4884,61 +4878,61 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▼ 34</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ESTC</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elastic-estc.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -4947,22 +4941,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-basf-adr-basfy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmarket-neu.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4974,40 +4968,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▼ 27</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-escalade-esca.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5019,40 +5013,40 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5064,40 +5058,40 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 16</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5109,40 +5103,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>▼ 27</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5154,52 +5148,52 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-geo-group-geo.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>CXW</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5208,31 +5202,31 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5244,130 +5238,130 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>ESTC</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▲ 14</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-carpenter-technology-crs.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>CSTM</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5379,12 +5373,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -5392,27 +5386,27 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5424,40 +5418,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 15</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5469,16 +5463,16 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -5487,67 +5481,67 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-flexsteel-industries-flxs.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>CIX</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5559,16 +5553,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -5577,67 +5571,67 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dupont-de-nemours-dd.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>BASFY</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5649,12 +5643,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5672,62 +5666,62 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
+          <t>PWR</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nyse-quanta-services-pwr.htm?symbolType=stock&amp;countryCode=us</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
           <t>IESC</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ies-holdings-iesc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>IESC</t>
-        </is>
-      </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5739,40 +5733,40 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5784,40 +5778,40 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>CSTM</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-constellium-cl-a-cstm.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>CRS</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5829,40 +5823,40 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5874,12 +5868,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -5887,27 +5881,27 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5919,40 +5913,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5964,40 +5958,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6009,40 +6003,40 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6054,40 +6048,40 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6099,16 +6093,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 4</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -6144,40 +6138,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6189,40 +6183,40 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6234,85 +6228,85 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>WEYS</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-weyco-group-weys.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6324,7 +6318,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -6333,31 +6327,31 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6369,12 +6363,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -6382,27 +6376,27 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6414,40 +6408,40 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6459,40 +6453,40 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>WEYS</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-weyco-group-weys.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>WEYS</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6504,7 +6498,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6513,31 +6507,31 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6549,85 +6543,85 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-shoals-technologies-group-shls.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6639,180 +6633,180 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>SHLS</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6822,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -6852,12 +6846,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>에러 발생</t>
+          <t>대기</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,11 +483,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -528,11 +528,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -573,11 +573,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -618,11 +618,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -641,17 +641,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-super-micro-computer-smci.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-super-micro-computer-smci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -663,11 +663,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -708,11 +708,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -753,11 +753,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -798,11 +798,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -821,17 +821,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marathon-petroleum-mpc.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marathon-petroleum-mpc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>UGP</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -888,11 +888,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -933,11 +933,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -978,11 +978,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1113,11 +1113,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-nvidia-nvda.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-nvidia-nvda.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1158,11 +1158,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1203,11 +1203,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1248,11 +1248,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1293,10 +1293,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>20</v>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>electrncs</t>
@@ -1336,11 +1338,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1359,17 +1361,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-williamssonoma-wsm.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-williamssonoma-wsm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1381,11 +1383,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1426,11 +1428,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1471,11 +1473,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1516,11 +1518,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1606,11 +1608,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1651,11 +1653,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1696,11 +1698,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1741,11 +1743,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1786,11 +1788,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>▼ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1831,35 +1833,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 33</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Banks-Savings &amp; Loan</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1876,40 +1878,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Banks-Savings &amp; Loan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-greene-county-bancorp-gcbc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ICAGY</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -1921,11 +1923,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1966,35 +1968,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2011,11 +2013,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2051,40 +2053,38 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>▼ 5</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>32</v>
-      </c>
+          <t>확인불가</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2096,40 +2096,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2141,40 +2141,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2186,85 +2186,85 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-nasdaq-ndaq.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-nasdaq-ndaq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2276,38 +2276,40 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>41</v>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-fox-corp-cl-a-foxa.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2319,40 +2321,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fox-corp-cl-a-foxa.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2364,40 +2366,40 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>▼ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2409,40 +2411,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>▲ 24</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2454,40 +2456,40 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2499,12 +2501,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2512,27 +2514,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xp-xp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2544,40 +2546,40 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xp-xp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2594,10 +2596,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>48</v>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>electrncs</t>
@@ -2615,33 +2619,33 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-celestica-cls.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-celestica-cls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>XMTR</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2677,38 +2681,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>▼ 2</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>48</v>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-sb-financial-group-sbfg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2720,40 +2726,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>▲ 19</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-sb-financial-group-sbfg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2765,7 +2771,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2774,31 +2780,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-shell-adr-shel.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2810,85 +2816,85 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>▼ 24</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-shell-adr-shel.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2900,85 +2906,85 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2990,85 +2996,85 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ITT</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>▼ 24</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-fastenal-fast.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3080,40 +3086,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fastenal-fast.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3125,85 +3131,85 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>META</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>GATX</t>
+          <t>META</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3215,40 +3221,40 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>▼ 18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3260,40 +3266,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3305,40 +3311,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3350,40 +3356,40 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3395,40 +3401,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SPNT</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-siriuspoint-spnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SPNT</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3440,40 +3446,40 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>SPNT</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-siriuspoint-spnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>SPNT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3485,85 +3491,85 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>▼ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CNI</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-canadian-national-railway-cni.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>CNI</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-canadian-national-railway-cni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>CNI</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3575,40 +3581,40 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3620,40 +3626,40 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3665,40 +3671,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3710,40 +3716,40 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3755,16 +3761,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>▲ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -3773,22 +3779,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3800,40 +3806,40 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>▼ 34</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>REPYY</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-repsol-adr-repyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>REPYY</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3845,40 +3851,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>▲ 12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>REPYY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-repsol-adr-repyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>REPYY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3890,40 +3896,40 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>▲ 9</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3935,40 +3941,40 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-marriott-international-mar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3980,40 +3986,40 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▲ 18</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4025,40 +4031,40 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4075,11 +4081,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -4115,40 +4121,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▲ 20</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-marriott-international-mar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4160,40 +4166,40 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4205,55 +4211,57 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>84</v>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -4261,27 +4269,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4293,40 +4301,40 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4338,40 +4346,40 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>▼ 25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4383,40 +4391,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4428,16 +4436,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -4473,40 +4481,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▼ 17</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ptc-ptc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4518,40 +4526,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>▲ 25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-flexsteel-industries-flxs.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ptc-ptc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4568,11 +4576,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>▼ 36</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -4581,22 +4589,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-flexsteel-industries-flxs.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4613,11 +4621,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -4658,11 +4666,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -4698,16 +4706,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -4748,11 +4756,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -4771,17 +4779,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jakks-pacific-jakk.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jakks-pacific-jakk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>ESCA</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
@@ -4793,11 +4801,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>▲ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -4838,11 +4846,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -4883,11 +4891,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -4923,40 +4931,40 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▼ 5</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmarket-neu.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4968,40 +4976,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmarket-neu.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5018,11 +5026,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -5058,40 +5066,40 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5103,40 +5111,40 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>▼ 27</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5148,85 +5156,85 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Security/Sfty</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-geo-group-geo.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>CXW</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Security/Sfty</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-geo-group-geo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5238,85 +5246,85 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ESTC</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>▲ 14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Computer Sftwr-Database</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5328,40 +5336,40 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5373,40 +5381,40 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>▲ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5418,40 +5426,40 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>▼ 15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5463,40 +5471,40 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5508,40 +5516,40 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>▼ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Consumer - Specialty</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>ODC</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5553,85 +5561,85 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dupont-de-nemours-dd.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>BASFY</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>▲ 11</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dupont-de-nemours-dd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5643,85 +5651,85 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-quanta-services-pwr.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>aerospace/defense</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aerospace/Defense</t>
+          <t>Bldg-Heavy Construction</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-quanta-services-pwr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5733,40 +5741,40 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>aerospace/defense</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Auto Parts</t>
+          <t>Aerospace/Defense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embraer-adr-embj.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>EMBJ</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5778,85 +5786,85 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>▼ 7</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Steel-Specialty Alloys</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CSTM</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-constellium-cl-a-cstm.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>CRS</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Food - Packaged</t>
+          <t>Steel-Specialty Alloys</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>CSTM</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-constellium-cl-a-cstm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>CSTM</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5868,40 +5876,40 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>▲ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Transportation-Logistics</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5913,40 +5921,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Food - Foodstuffs</t>
+          <t>Transportation-Logistics</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-expeditors-international-of-washington-expd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>TATYY</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5958,40 +5966,40 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Royalty Trust</t>
+          <t>Food - Foodstuffs</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-tate-and-lyle-adr-tatyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>PVL</t>
+          <t>TATYY</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6003,40 +6011,40 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Transportation-Truck</t>
+          <t>Oil&amp;Gas-Royalty Trust</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-permianville-royalty-trust-pvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>PVL</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6048,40 +6056,40 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Transportation-Truck</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jb-hunt-transport-services-jbht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ELPC</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6093,40 +6101,40 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>▲ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>utility</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Trucks &amp; Parts-Hvy Duty</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-companhia-paranaense-de-energiacopel-adr-elpc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>MLR</t>
+          <t>ELPC</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6138,40 +6146,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Estate Dvlpmt/Ops</t>
+          <t>Trucks &amp; Parts-Hvy Duty</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-jones-lang-lasalle-jll.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-miller-industries-mlr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>MLR</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6183,85 +6191,85 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>▼ 10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chemicals-Plastics</t>
+          <t>Real Estate Dvlpmt/Ops</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-st-joe-joe.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>AVNT</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Leisure-Movies &amp; Related</t>
+          <t>Chemicals-Plastics</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-avient-avnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>AVNT</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6273,40 +6281,40 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Bldg Prds</t>
+          <t>Leisure-Movies &amp; Related</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-imax-imax.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>GIC</t>
+          <t>IMAX</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6318,16 +6326,16 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -6336,22 +6344,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Retail-Super/Mini Mkts</t>
+          <t>Retail/Whlsle-Bldg Prds</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-global-industrial-gic.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ASAIY</t>
+          <t>GIC</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6363,16 +6371,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>▲ 5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -6381,22 +6389,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Retail-Leisure Products</t>
+          <t>Retail-Super/Mini Mkts</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-sendas-distribuidora-adr-asaiy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>ASAIY</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6408,40 +6416,40 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>▲ 6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bldg-Cement/Concrt/Ag</t>
+          <t>Retail-Leisure Products</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-marinemax-hzo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>CPAC</t>
+          <t>HZO</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6453,12 +6461,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -6466,27 +6474,27 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Apparel - Clothing &amp; Shoes</t>
+          <t>Bldg-Cement/Concrt/Ag</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>WEYS</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-weyco-group-weys.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cementos-pacasmayo-adr-cpac.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>WEYS</t>
+          <t>CPAC</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6498,40 +6506,40 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>▼ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Retail-Restaurants</t>
+          <t>Apparel - Clothing &amp; Shoes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>WEYS</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-weyco-group-weys.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>EAT</t>
+          <t>WEYS</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6543,7 +6551,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6552,31 +6560,31 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Specialty Enterprise</t>
+          <t>Retail-Restaurants</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-brinker-international-eat.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>EAT</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6588,40 +6596,40 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>137</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Finance-Mrtg&amp;Rel Svc</t>
+          <t>Comp Sftwr - Specialty Enterprise</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-descartes-systems-group-dsgx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6633,40 +6641,40 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Leisure-Gaming/Equip</t>
+          <t>Finance-Mrtg&amp;Rel Svc</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-federal-agricultural-mortgage-cl-c-agm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>EVVTY</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6678,40 +6686,40 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>▼ 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Financial</t>
+          <t>Leisure-Gaming/Equip</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-evolution-gaming-group-adr-evvty.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>ACIW</t>
+          <t>EVVTY</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6723,7 +6731,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6732,43 +6740,43 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Energy-Solar</t>
+          <t>Comp Sftwr - Financial</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-aci-worldwide-aciw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>SHLS</t>
+          <t>ACIW</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>141</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6777,31 +6785,31 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bldg-Maintenance &amp; Svc</t>
+          <t>Energy-Solar</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-first-solar-fslr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6813,45 +6821,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bldg-Maintenance &amp; Svc</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mistras-group-mg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>대기</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -1833,11 +1833,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>▲ 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2058,10 +2058,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>36</v>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>finance</t>
@@ -2641,11 +2643,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2686,11 +2688,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2776,11 +2778,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2866,11 +2868,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3586,11 +3588,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3676,11 +3678,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3991,11 +3993,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>▲ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4126,11 +4128,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>▼ 2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -4441,11 +4443,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -4486,11 +4488,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4711,11 +4713,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>▲ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -4936,11 +4938,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>▼ 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -5071,11 +5073,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>▼ 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -6219,17 +6221,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-st-joe-joe.htm?symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-st-joe-joe.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>성공 (새 1위 포착)</t>
+          <t>성공 (현재 티커 1위 유지)</t>
         </is>
       </c>
     </row>

--- a/IBD_Updated_Top1_Groups.xlsx
+++ b/IBD_Updated_Top1_Groups.xlsx
@@ -483,35 +483,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Medical</t>
+          <t>Medical - Research</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -528,35 +528,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Medical - Research</t>
+          <t>Business Equip &amp; Supplies</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-illumina-ilmn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -573,35 +573,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Business Equip &amp; Supplies</t>
+          <t>Computer Sftwr-Medical</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-zebra-technologies-cl-a-zbra.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-veeva-systems-cl-a-veev.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -618,35 +618,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Computer-Hardware/Perip</t>
+          <t>Computer Sftwr-Security</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-super-micro-computer-smci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -663,35 +663,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Comp Sftwr - Enterprise</t>
+          <t>Medical-Services</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -703,40 +703,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medical-Services</t>
+          <t>Comml Svcs-Staffing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-caredx-cdna.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>RCRUY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -757,76 +757,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Security</t>
+          <t>Oil&amp;Gas-Refining/Mktg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>UGP</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-palo-alto-networks-panw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ultrapar-participacoes-adr-ugp.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Refining/Mktg</t>
+          <t>Comp Sftwr - Enterprise</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-marathon-petroleum-mpc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-microsoft-msft.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -838,40 +838,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Comml Svcs-Staffing</t>
+          <t>Hsehold-Appliances/Wares</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-recruit-holdings-adr-rcruy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>RCRUY</t>
+          <t>SN</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -933,35 +933,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Telecom-Consumer Prods</t>
+          <t>Computer-Hardware/Perip</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-super-micro-computer-smci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -978,35 +978,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hsehold-Appliances/Wares</t>
+          <t>Transport - Oil/Gas Shipping</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-sharkninja-sn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1023,35 +1023,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>chips</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Elec-Semiconductor Mfg</t>
+          <t>Telecom-Consumer Prods</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-apple-aapl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Transport - Oil/Gas Shipping</t>
+          <t>Transportation-Ship</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dht-holdings-dht.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-okeanis-eco-tankers-eco.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1158,35 +1158,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>chips</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>Elec-Semiconductor Mfg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-taiwan-semiconductor-manufacturing-adr-tsm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1203,35 +1203,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Transportation-Ship</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-okeanis-eco-tankers-eco.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-cronos-group-cron.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1261,22 +1261,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Electronic-Parts</t>
+          <t>Elec-Scientific/Msrng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1293,11 +1293,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1306,22 +1306,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elec-Scientific/Msrng</t>
+          <t>Electronic-Parts</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-keysight-technologies-keys.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amphenol-cl-a-aph.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1338,35 +1338,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Retail - Home Furnishings/Electronics</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-williamssonoma-wsm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1378,40 +1378,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Computer-Networking</t>
+          <t>Medical - Profitable Biotech</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1423,40 +1423,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Banks-Foreign</t>
+          <t>Retail - Home Furnishings/Electronics</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VBNK</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-versabank-vbnk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-williamssonoma-wsm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>VBNK</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1468,40 +1468,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Computer-Networking</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-arista-networks-anet.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1531,22 +1531,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medical - Profitable Biotech</t>
+          <t>Medical - Pharmaceuticals</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-halozyme-therapeutics-halo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1563,35 +1563,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medical - Pharmaceuticals</t>
+          <t>Transportation-Equip Mfg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-eli-lilly-lly.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>TWIN</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1608,80 +1608,80 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Machinery-Constr/Mining/Farming</t>
+          <t>Banks-Foreign</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>UOVEY</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-united-overseas-bank-adr-uovey.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MTW</t>
+          <t>VBNK</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Banks-Money Center</t>
+          <t>Medical - Home &amp; Nursing Care</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-dbs-group-holdings-adr-dbsdy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>PNTG</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1743,35 +1743,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Finance - Crypto/Blockchain</t>
+          <t>Machinery-Constr/Mining/Farming</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-manitowoc-mtw.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>MTW</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1788,35 +1788,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Internet-Network Sltns</t>
+          <t>Finance - Crypto/Blockchain</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-cypherpunk-technologies-cyph.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1833,35 +1833,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elec-Misc Products</t>
+          <t>Oil&amp;Gas-Integrated</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-shell-adr-shel.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1923,40 +1923,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Edu/Media</t>
+          <t>Banks-Money Center</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mitsubishi-ufj-financial-group-adr-mufg.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>DBSDY</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -1968,35 +1968,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Transportation-Airline</t>
+          <t>Diversified Operations</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-johnson-controls-international-jci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>JAPSY</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2013,40 +2013,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 7</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>media</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Diversified Operations</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-johnson-controls-international-jci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fox-corp-cl-b-fox.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>FOXA</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2058,40 +2058,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finance-CrdtCard/PmtPr</t>
+          <t>Medical-Systems</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-waters-wat.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2103,35 +2103,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Steel-Producers</t>
+          <t>Finance-CrdtCard/PmtPr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-paysign-pays.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2161,22 +2161,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Transportation-Equip Mfg</t>
+          <t>Transportation-Airline</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-twin-disc-twin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-japan-airlines-adr-japsy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>TWIN</t>
+          <t>JAPSY</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2193,40 +2193,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 24</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medical - Home &amp; Nursing Care</t>
+          <t>Tobacco</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-pennant-group-pntg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-philip-morris-international-pm.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>JAPAY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -2238,35 +2238,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Financial Svcs-Specialty</t>
+          <t>Beverages-Non-Alcoholic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-nasdaq-ndaq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>AKO.A</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2283,35 +2283,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Beverages-Non-Alcoholic</t>
+          <t>Financial Svcs-Specialty</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-embotelladora-andina-sa-series-a-adr-ako.a.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-nasdaq-ndaq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>AKO.A</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2328,35 +2328,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 17</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>media</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Retail - Specialty</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-fox-corp-cl-a-foxa.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-fastenal-fast.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2373,35 +2373,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 6</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Telecom - Equipment</t>
+          <t>Steel-Producers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-hongli-group-hlp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>HLP</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2418,35 +2418,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Finance-Commercial Loans</t>
+          <t>Comml Svcs-Outsourcing</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 10</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2476,22 +2476,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medical-Hospitals</t>
+          <t>Medical-Managed Care</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2508,35 +2508,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Comml Svcs-Outsourcing</t>
+          <t>Medical-Hospitals</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-red-violet-rdvt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-nutex-health-nutx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>NUTX</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2553,35 +2553,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 17</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Finance-Invest Bnk/Bkrs</t>
+          <t>Internet-Network Sltns</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-xp-xp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-f5-ffiv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>XP</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2598,35 +2598,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>electrncs</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Elec-Contract Mfg</t>
+          <t>Finance-Invest Bnk/Bkrs</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-celestica-cls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-xp-xp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CLS</t>
+          <t>XP</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2643,35 +2643,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Building - Tools</t>
+          <t>Elec-Contract Mfg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-stanley-black-and-decker-swk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-celestica-cls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CLS</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2688,35 +2688,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 21</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mining-Metal Ores</t>
+          <t>Medical - Development Biotech</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ERO</t>
+          <t>PLX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2733,35 +2733,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Banks-Regional</t>
+          <t>Mining-Metal Ores</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-sb-financial-group-sbfg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ero-copper-ero.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SBFG</t>
+          <t>ERO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2778,35 +2778,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Integrated</t>
+          <t>Finance-Commercial Loans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-shell-adr-shel.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-medallion-financial-mfin.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2823,35 +2823,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 20</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Telecom-Infrastructure</t>
+          <t>Computer Sftwr-Edu/Media</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-spotify-technology-spot.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2868,35 +2868,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Machinery-Mtl Hdlg/Autmn</t>
+          <t>Containers/Packaging</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2913,35 +2913,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Medical-Managed Care</t>
+          <t>Machinery-Mtl Hdlg/Autmn</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-corvel-crvl.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-materialise-adr-mtls.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2953,40 +2953,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 26</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>mining</t>
+          <t>electrncs</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mining-Gold/Silver/Gems</t>
+          <t>Elec-Misc Products</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-wheaton-precious-metals-wpm.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-espey-manufacturing-and-electronics-esp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>WPM</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3003,40 +3003,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Medical-Systems</t>
+          <t>Building - Tools</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>TTC</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-mesa-laboratories-mlab.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-toro-ttc.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3048,35 +3048,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 11</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Machinery-Gen Industrial</t>
+          <t>Transportation-Rail</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>CNI</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-canadian-national-railway-cni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>CNI</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3093,35 +3093,35 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 16</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Retail - Specialty</t>
+          <t>Telecom - Equipment</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-fastenal-fast.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-lumentum-holdings-lite.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3138,35 +3138,35 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 1</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Internet-Content</t>
+          <t>Comml Svcs-Leasing</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AER</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3183,40 +3183,40 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Comml Svcs-Leasing</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-aercap-holdings-aer.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-reinsurance-group-of-america-rga.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>AER</t>
+          <t>SPNT</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3228,35 +3228,35 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Containers/Packaging</t>
+          <t>Banks-Regional</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-karat-packaging-krt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-sb-financial-group-sbfg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>SBFG</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3273,35 +3273,35 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tobacco</t>
+          <t>Machinery-Gen Industrial</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-japan-tobacco-adr-japay.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-proto-labs-prlb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>JAPAY</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3318,35 +3318,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Electrical-Power/Equipmt</t>
+          <t>Telecom-Infrastructure</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ubiquiti-ui.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3363,35 +3363,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 23</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>misc</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Paper &amp; Paper Products</t>
+          <t>Cosmetics/Personal Care</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>MATV</t>
+          <t>ELF</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3408,35 +3408,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Finance-Consumer Loans</t>
+          <t>Leisure-Lodging</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-atlanticus-holdings-atlc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-marriott-international-mar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ATLC</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3453,35 +3453,35 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Internet-Content</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SPNT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-siriuspoint-spnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-meta-platforms-meta.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SPNT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3498,35 +3498,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 8</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>alcohl/tob/thc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Beverages-Alcoholic</t>
+          <t>Oil&amp;Gas-Explorers/Producers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>REPYY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-repsol-adr-repyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>KNBWY</t>
+          <t>REPYY</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3543,35 +3543,35 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 5</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Transportation-Rail</t>
+          <t>Electrical-Power/Equipmt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CNI</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-canadian-national-railway-cni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-allient-alnt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CNI</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3588,35 +3588,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>metals</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Finance-Investment Mgmt</t>
+          <t>Metal Products - Distributors/Fabrication</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>VCTR</t>
+          <t>FRD</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3633,35 +3633,35 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Medical - Development Biotech</t>
+          <t>Pollution Control</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-amer-protalix-biotherapeutics-plx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>PLX</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3678,40 +3678,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>real est</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ltc-properties-ltc.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>CRESY</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3723,40 +3723,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 22</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>metals</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Metal Products - Distributors/Fabrication</t>
+          <t>Medical-Products</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-friedman-industries-frd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-dexcom-dxcm.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>FRD</t>
+          <t>PDEX</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3768,35 +3768,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 12</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Retail-Internet</t>
+          <t>Food - Wholesale</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>LQDT</t>
+          <t>USFD</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3813,35 +3813,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>misc</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Retail/Whlsle-Automobile</t>
+          <t>Paper &amp; Paper Products</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mativ-holdings-matv.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>MATV</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3858,40 +3858,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Explorers/Producers</t>
+          <t>Finance-Consumer Loans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>REPYY</t>
+          <t>IX</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-repsol-adr-repyy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-orix-adr-ix.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>REPYY</t>
+          <t>ATLC</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3903,40 +3903,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 21</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>mining</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Banks-Super Regional</t>
+          <t>Mining-Gold/Silver/Gems</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>FSM</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fortuna-mining-fsm.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>ESQ</t>
+          <t>WPM</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -3948,35 +3948,35 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Comml Svcs-Advertising</t>
+          <t>Retail-Internet</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liquidity-services-lqdt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MGNI</t>
+          <t>LQDT</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3993,35 +3993,35 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Medical-Distribution</t>
+          <t>Banks-Super Regional</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-esquire-financial-holdings-esq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>ESQ</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4038,35 +4038,35 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bldg-Resident/Comml</t>
+          <t>Finance-Investment Mgmt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-victory-capital-holdings-cl-a-vctr.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>VCTR</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>alcohl/tob/thc</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Energy-Coal</t>
+          <t>Beverages-Alcoholic</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-glencore-adr-glncy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/otherotc-kirin-holdings-adr-knbwy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>GLNCY</t>
+          <t>KNBWY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4128,35 +4128,35 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Leisure-Lodging</t>
+          <t>Medical-Distribution</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-marriott-international-mar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-mckesson-mck.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4173,11 +4173,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -4186,22 +4186,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Building - Construction Products</t>
+          <t>Bldg-Resident/Comml</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-comstock-holding-cl-a-chci.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4218,35 +4218,35 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 1</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>real est</t>
+          <t>building</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Building - Construction Products</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-cresud-adr-cresy.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-interface-tile.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>CRESY</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4263,40 +4263,40 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Computer-Tech Services</t>
+          <t>Energy-Coal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-warrior-met-coal-hcc.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>GCT</t>
+          <t>GLNCY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -4308,35 +4308,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 19</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>food/bev</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Food - Wholesale</t>
+          <t>Computer Sftwr-Gaming</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-us-foods-holding-usfd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>USFD</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4353,35 +4353,35 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Telecom Svcs- Foreign</t>
+          <t>Leisure-Products</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-jakks-pacific-jakk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>JAKK</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4398,35 +4398,35 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cosmetics/Personal Care</t>
+          <t>Chemicals-Specialty</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-elf-beauty-elf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-newmarket-neu.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>ELF</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4443,11 +4443,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 11</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -4456,22 +4456,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Comml Svcs-Market Rsrch</t>
+          <t>Comml Svcs-Advertising</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-magnite-mgni.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4488,35 +4488,35 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pollution Control</t>
+          <t>Oil&amp;Gas - Pipeline</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-permapipe-international-holdings-ppih.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4533,35 +4533,35 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 13</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Design</t>
+          <t>Retail - General</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-ptc-ptc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4578,35 +4578,35 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hsehold/Office Furniture</t>
+          <t>Computer-Tech Services</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-flexsteel-industries-flxs.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-gigacloud-technology-gct.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4623,35 +4623,35 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>software</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Machinery/Equip</t>
+          <t>Computer Sftwr-Design</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-ptc-ptc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>FTI</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4668,35 +4668,35 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 7</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>busins svc</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Comml Svcs-Consulting</t>
+          <t>Telecom Svcs- Foreign</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-liberty-latin-america-cl-c-lilak.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>HURN</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4713,35 +4713,35 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Medical-Products</t>
+          <t>Oil&amp;Gas-Machinery/Equip</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-prodex-pdex.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-technipfmc-fti.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>PDEX</t>
+          <t>FTI</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4758,35 +4758,35 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 2</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Leisure-Products</t>
+          <t>Comml Svcs-Consulting</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-jakks-pacific-jakk.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-huron-consulting-group-hurn.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>HURN</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4803,35 +4803,35 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 25</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Energy-Alternative/Other</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-ferrari-race.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>VWDRY</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4848,35 +4848,35 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 9</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>busins svc</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Field Services</t>
+          <t>Comml Svcs-Market Rsrch</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-niq-global-intelligence-niq.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>OII</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4893,35 +4893,35 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>telecom</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Auto/Truck Equipment Parts &amp; Tires</t>
+          <t>Telecom/Cable Services</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>IDT</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4938,35 +4938,35 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 16</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Consumer Svcs-Education</t>
+          <t>Transport-Air Freight</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4983,35 +4983,35 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 6</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chemicals-Specialty</t>
+          <t>Retail-Apparel/Shoes/Acc</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-newmarket-neu.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5028,35 +5028,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>telecom</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Telecom/Cable Services</t>
+          <t>Oil&amp;Gas-Field Services</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-idt-cl-b-idt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-oceaneering-international-oii.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>IDT</t>
+          <t>OII</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5073,35 +5073,35 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 28</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas - Pipeline</t>
+          <t>Retail/Whlsle-Automobile</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-targa-resources-trgp.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-rush-enterprises-cl-b-rushb.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5118,40 +5118,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 5</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Retail - General</t>
+          <t>Leisure-Travel Booking</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-five-below-five.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-expedia-group-expe.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>TRVG</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5163,40 +5163,40 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 13</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Gaming</t>
+          <t>Hsehold/Office Furniture</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CIX</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-doubledown-interactive-adr-ddi.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-amer-compx-international-cl-a-cix.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5226,22 +5226,22 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
+          <t>ALRM</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://research.investors.com/stock-quotes/nasdaq-alarmcom-holdings-alrm.htm?symbolType=stock&amp;countryCode=us</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
           <t>GEO</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://research.investors.com/stock-quotes/nyse-geo-group-geo.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>GEO</t>
-        </is>
-      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5253,35 +5253,35 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Retail-Apparel/Shoes/Acc</t>
+          <t>Agricultural Operations</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-abercrombie-and-fitch-anf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5298,35 +5298,35 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 8</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>software</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Computer Sftwr-Database</t>
+          <t>Consumer Svcs-Education</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-commvault-systems-cvlt.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-tal-education-group-adr-tal.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5343,35 +5343,35 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 10</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Leisure-Travel Booking</t>
+          <t>Auto/Truck Equipment Parts &amp; Tires</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nasdaq-trivago-adr-trvg.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-china-automotive-systems-caas.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>TRVG</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5388,35 +5388,35 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Agricultural Operations</t>
+          <t>Retail/Whlsle-Auto Parts</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-darling-ingredients-dar.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/ncm-carpartscom-prts.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5433,35 +5433,35 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 3</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>leisure</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Leisure-Services</t>
+          <t>Chemicals-Agricultural</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-life-time-group-holdings-lth.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5478,35 +5478,35 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 9</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>food/bev</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oil&amp;Gas-Drilling</t>
+          <t>Food - Packaged</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nasdaq-chefs-warehouse-chef.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>CHEF</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5523,35 +5523,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▲ 2</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>consumer</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Consumer - Specialty</t>
+          <t>Chemicals-Basic</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-oildri-of-america-odc.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-dupont-de-nemours-dd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ODC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5568,40 +5568,40 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 3</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chemicals-Agricultural</t>
+          <t>Leisure-Services</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>CNK</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-cf-industries-holdings-cf.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-cinemark-holdings-cnk.htm?symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>성공 (현재 티커 1위 유지)</t>
+          <t>성공 (새 1위 포착)</t>
         </is>
       </c>
     </row>
@@ -5613,35 +5613,35 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 18</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>chemical</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chemicals-Basic</t>
+          <t>Energy-Alternative/Other</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-dupont-de-nemours-dd.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/pinksh-vestas-wind-systems-adr-vwdry.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VWDRY</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5658,35 +5658,35 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Transport-Air Freight</t>
+          <t>Oil&amp;Gas-Drilling</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://research.investors.com/stock-quotes/nyse-fedex-fdx.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
+          <t>https://research.investors.com/stock-quotes/nyse-valaris-val.htm?fromsearch=1&amp;list=&amp;symbolType=stock&amp;countryCode=us</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>VAL</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5703,35 +5703,35 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>▼ 4</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>building</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bldg-Heavy Construction</t>
+          <t>Consumer - Specialty